--- a/运气工程/运气工程-05-SlotsRTP计算规则-WILD篇.xlsx
+++ b/运气工程/运气工程-05-SlotsRTP计算规则-WILD篇.xlsx
@@ -2188,6 +2188,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J87" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3480,6 +3483,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M67" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5805,6 +5811,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:V60" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8360,6 +8369,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:T71" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -11944,5 +11956,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:W81" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/运气工程/运气工程-05-SlotsRTP计算规则-WILD篇.xlsx
+++ b/运气工程/运气工程-05-SlotsRTP计算规则-WILD篇.xlsx
@@ -694,11 +694,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1406,7 +1407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1452,6 +1453,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3775,7 +3780,7 @@
         <f>VLOOKUP($A5,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P5" s="17">
+      <c r="P5" s="31">
         <f>(J5*M5+K5*N5+L5*O5)/滚轴与赔付!$H$25</f>
         <v>0.011615625</v>
       </c>
@@ -3843,7 +3848,7 @@
         <f>VLOOKUP($A6,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P6" s="17">
+      <c r="P6" s="31">
         <f>(J6*M6+K6*N6+L6*O6)/滚轴与赔付!$H$25</f>
         <v>0.0326953125</v>
       </c>
@@ -3911,7 +3916,7 @@
         <f>VLOOKUP($A7,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P7" s="17">
+      <c r="P7" s="31">
         <f>(J7*M7+K7*N7+L7*O7)/滚轴与赔付!$H$25</f>
         <v>0.102</v>
       </c>
@@ -3979,7 +3984,7 @@
         <f>VLOOKUP($A8,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="31">
         <f>(J8*M8+K8*N8+L8*O8)/滚轴与赔付!$H$25</f>
         <v>0.0765</v>
       </c>
@@ -4047,7 +4052,7 @@
         <f>VLOOKUP($A9,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P9" s="17">
+      <c r="P9" s="31">
         <f>(J9*M9+K9*N9+L9*O9)/滚轴与赔付!$H$25</f>
         <v>0.0912</v>
       </c>
@@ -4104,7 +4109,7 @@
       <c r="O10" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="18">
+      <c r="P10" s="32">
         <f>SUM(P5:P9)</f>
         <v>0.3140109375</v>
       </c>
@@ -4331,7 +4336,7 @@
         <f>VLOOKUP($A14,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P14" s="17">
+      <c r="P14" s="31">
         <f>(J14*M14+K14*N14+L14*O14)/滚轴与赔付!$H$25</f>
         <v>0.0256</v>
       </c>
@@ -4399,7 +4404,7 @@
         <f>VLOOKUP($A15,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="31">
         <f>(J15*M15+K15*N15+L15*O15)/滚轴与赔付!$H$25</f>
         <v>0.072</v>
       </c>
@@ -4467,7 +4472,7 @@
         <f>VLOOKUP($A16,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P16" s="17">
+      <c r="P16" s="31">
         <f>(J16*M16+K16*N16+L16*O16)/滚轴与赔付!$H$25</f>
         <v>0.1828125</v>
       </c>
@@ -4535,7 +4540,7 @@
         <f>VLOOKUP($A17,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P17" s="17">
+      <c r="P17" s="31">
         <f>(J17*M17+K17*N17+L17*O17)/滚轴与赔付!$H$25</f>
         <v>0.15234375</v>
       </c>
@@ -4603,7 +4608,7 @@
         <f>VLOOKUP($A18,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P18" s="17">
+      <c r="P18" s="31">
         <f>(J18*M18+K18*N18+L18*O18)/滚轴与赔付!$H$25</f>
         <v>0.1640625</v>
       </c>
@@ -4660,7 +4665,7 @@
       <c r="O19" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="P19" s="18">
+      <c r="P19" s="32">
         <f>SUM(P14:P18)</f>
         <v>0.59681875</v>
       </c>
@@ -4887,7 +4892,7 @@
         <f>VLOOKUP($A23,滚轴与赔付!$A$41:$D$46,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P23" s="17">
+      <c r="P23" s="31">
         <f>(J23*M23+K23*N23+L23*O23)/滚轴与赔付!$H$25</f>
         <v>0</v>
       </c>
@@ -4944,7 +4949,7 @@
       <c r="O24" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="P24" s="18">
+      <c r="P24" s="32">
         <f>SUM(P23)</f>
         <v>0</v>
       </c>
@@ -5068,7 +5073,7 @@
       <c r="C27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="32">
         <f>P10</f>
         <v>0.3140109375</v>
       </c>
@@ -5122,7 +5127,7 @@
       <c r="C28" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="32">
         <f>P19-P10</f>
         <v>0.2828078125</v>
       </c>
@@ -5176,7 +5181,7 @@
       <c r="C29" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="32">
         <f>P24</f>
         <v>0</v>
       </c>
@@ -5230,7 +5235,7 @@
       <c r="C30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="32">
         <f>D27+D28+D29</f>
         <v>0.59681875</v>
       </c>
@@ -5284,7 +5289,7 @@
       <c r="C31" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="31">
         <f>滚轴与赔付!$B$47*(10*0.15^3*0.85^2+5*0.15^4*0.85+0.15^5)</f>
         <v>0.05322375</v>
       </c>
@@ -5338,7 +5343,7 @@
       <c r="C32" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="32">
         <f>D30+D31</f>
         <v>0.6500425</v>
       </c>
@@ -5657,7 +5662,7 @@
       <c r="C38" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="32">
         <f>D35+D36+D37</f>
         <v>1.4197</v>
       </c>
@@ -6850,7 +6855,7 @@
         <f t="shared" ref="B21:B41" si="0">SUMPRODUCT(($B$11:$B$15*(1-$A21/20)+$A21)*$O$11:$O$15)</f>
         <v>1909820</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="32">
         <f>B21/滚轴与赔付!$H$25</f>
         <v>0.59681875</v>
       </c>
@@ -6900,7 +6905,7 @@
         <f t="shared" si="0"/>
         <v>2304299</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="32">
         <f>B22/滚轴与赔付!$H$25</f>
         <v>0.7200934375</v>
       </c>
@@ -6950,7 +6955,7 @@
         <f t="shared" si="0"/>
         <v>2698778</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="32">
         <f>B23/滚轴与赔付!$H$25</f>
         <v>0.843368125</v>
       </c>
@@ -7000,7 +7005,7 @@
         <f t="shared" si="0"/>
         <v>3093257</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="32">
         <f>B24/滚轴与赔付!$H$25</f>
         <v>0.9666428125</v>
       </c>
@@ -7050,7 +7055,7 @@
         <f t="shared" si="0"/>
         <v>3487736</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="32">
         <f>B25/滚轴与赔付!$H$25</f>
         <v>1.0899175</v>
       </c>
@@ -7100,7 +7105,7 @@
         <f t="shared" si="0"/>
         <v>3882215</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="32">
         <f>B26/滚轴与赔付!$H$25</f>
         <v>1.2131921875</v>
       </c>
@@ -7150,7 +7155,7 @@
         <f t="shared" si="0"/>
         <v>4276694</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="32">
         <f>B27/滚轴与赔付!$H$25</f>
         <v>1.336466875</v>
       </c>
@@ -7200,7 +7205,7 @@
         <f t="shared" si="0"/>
         <v>4671173</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="32">
         <f>B28/滚轴与赔付!$H$25</f>
         <v>1.4597415625</v>
       </c>
@@ -7250,7 +7255,7 @@
         <f t="shared" si="0"/>
         <v>5065652</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="32">
         <f>B29/滚轴与赔付!$H$25</f>
         <v>1.58301625</v>
       </c>
@@ -7300,7 +7305,7 @@
         <f t="shared" si="0"/>
         <v>5460131</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="32">
         <f>B30/滚轴与赔付!$H$25</f>
         <v>1.7062909375</v>
       </c>
@@ -7350,7 +7355,7 @@
         <f t="shared" si="0"/>
         <v>5854610</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="32">
         <f>B31/滚轴与赔付!$H$25</f>
         <v>1.829565625</v>
       </c>
@@ -7400,7 +7405,7 @@
         <f t="shared" si="0"/>
         <v>6249089</v>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="32">
         <f>B32/滚轴与赔付!$H$25</f>
         <v>1.9528403125</v>
       </c>
@@ -7450,7 +7455,7 @@
         <f t="shared" si="0"/>
         <v>6643568</v>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="32">
         <f>B33/滚轴与赔付!$H$25</f>
         <v>2.076115</v>
       </c>
@@ -7500,7 +7505,7 @@
         <f t="shared" si="0"/>
         <v>7038047</v>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="32">
         <f>B34/滚轴与赔付!$H$25</f>
         <v>2.1993896875</v>
       </c>
@@ -7550,7 +7555,7 @@
         <f t="shared" si="0"/>
         <v>7432526</v>
       </c>
-      <c r="C35" s="18">
+      <c r="C35" s="32">
         <f>B35/滚轴与赔付!$H$25</f>
         <v>2.322664375</v>
       </c>
@@ -7600,7 +7605,7 @@
         <f t="shared" si="0"/>
         <v>7827005</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="32">
         <f>B36/滚轴与赔付!$H$25</f>
         <v>2.4459390625</v>
       </c>
@@ -7650,7 +7655,7 @@
         <f t="shared" si="0"/>
         <v>8221484</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="32">
         <f>B37/滚轴与赔付!$H$25</f>
         <v>2.56921375</v>
       </c>
@@ -7700,7 +7705,7 @@
         <f t="shared" si="0"/>
         <v>8615963</v>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="32">
         <f>B38/滚轴与赔付!$H$25</f>
         <v>2.6924884375</v>
       </c>
@@ -7750,7 +7755,7 @@
         <f t="shared" si="0"/>
         <v>9010442</v>
       </c>
-      <c r="C39" s="18">
+      <c r="C39" s="32">
         <f>B39/滚轴与赔付!$H$25</f>
         <v>2.815763125</v>
       </c>
@@ -7800,7 +7805,7 @@
         <f t="shared" si="0"/>
         <v>9404921</v>
       </c>
-      <c r="C40" s="18">
+      <c r="C40" s="32">
         <f>B40/滚轴与赔付!$H$25</f>
         <v>2.9390378125</v>
       </c>
@@ -7850,7 +7855,7 @@
         <f t="shared" si="0"/>
         <v>9799400</v>
       </c>
-      <c r="C41" s="18">
+      <c r="C41" s="32">
         <f>B41/滚轴与赔付!$H$25</f>
         <v>3.0623125</v>
       </c>
@@ -7993,7 +7998,7 @@
       <c r="B44" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="32">
         <f>C21</f>
         <v>0.59681875</v>
       </c>
@@ -8041,7 +8046,7 @@
       <c r="B45" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="32">
         <f>C41</f>
         <v>3.0623125</v>
       </c>
@@ -9583,7 +9588,7 @@
       <c r="B22" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="31">
         <f>RTP分解!$D$28</f>
         <v>0.2828078125</v>
       </c>
@@ -9640,7 +9645,7 @@
       <c r="B23" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="32">
         <f>C22*$B$20</f>
         <v>0.7353003125</v>
       </c>
@@ -9697,7 +9702,7 @@
       <c r="B24" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="32">
         <f>RTP分解!$D$27+C23+RTP分解!$D$29</f>
         <v>1.04931125</v>
       </c>
@@ -10256,15 +10261,15 @@
         <f>VLOOKUP($A33,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P33" s="17">
+      <c r="P33" s="31">
         <f>RTP分解!$P$14</f>
         <v>0.0256</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="31">
         <f>(J33*M33+K33*N33+L33*O33)/滚轴与赔付!$H$25</f>
         <v>0.128</v>
       </c>
-      <c r="R33" s="17">
+      <c r="R33" s="31">
         <f>(1-$B$31)*P33+$B$31*Q33</f>
         <v>0.04096</v>
       </c>
@@ -10329,15 +10334,15 @@
         <f>VLOOKUP($A34,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P34" s="17">
+      <c r="P34" s="31">
         <f>RTP分解!$P$15</f>
         <v>0.072</v>
       </c>
-      <c r="Q34" s="17">
+      <c r="Q34" s="31">
         <f>(J34*M34+K34*N34+L34*O34)/滚轴与赔付!$H$25</f>
         <v>0.36</v>
       </c>
-      <c r="R34" s="17">
+      <c r="R34" s="31">
         <f>(1-$B$31)*P34+$B$31*Q34</f>
         <v>0.1152</v>
       </c>
@@ -10402,15 +10407,15 @@
         <f>VLOOKUP($A35,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P35" s="17">
+      <c r="P35" s="31">
         <f>RTP分解!$P$16</f>
         <v>0.1828125</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="Q35" s="31">
         <f>(J35*M35+K35*N35+L35*O35)/滚轴与赔付!$H$25</f>
         <v>0.73125</v>
       </c>
-      <c r="R35" s="17">
+      <c r="R35" s="31">
         <f>(1-$B$31)*P35+$B$31*Q35</f>
         <v>0.265078125</v>
       </c>
@@ -10475,15 +10480,15 @@
         <f>VLOOKUP($A36,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P36" s="17">
+      <c r="P36" s="31">
         <f>RTP分解!$P$17</f>
         <v>0.15234375</v>
       </c>
-      <c r="Q36" s="17">
+      <c r="Q36" s="31">
         <f>(J36*M36+K36*N36+L36*O36)/滚轴与赔付!$H$25</f>
         <v>0.609375</v>
       </c>
-      <c r="R36" s="17">
+      <c r="R36" s="31">
         <f>(1-$B$31)*P36+$B$31*Q36</f>
         <v>0.2208984375</v>
       </c>
@@ -10548,15 +10553,15 @@
         <f>VLOOKUP($A37,滚轴与赔付!$A$41:$D$45,2,FALSE())</f>
         <v>5</v>
       </c>
-      <c r="P37" s="17">
+      <c r="P37" s="31">
         <f>RTP分解!$P$18</f>
         <v>0.1640625</v>
       </c>
-      <c r="Q37" s="17">
+      <c r="Q37" s="31">
         <f>(J37*M37+K37*N37+L37*O37)/滚轴与赔付!$H$25</f>
         <v>0.65625</v>
       </c>
-      <c r="R37" s="17">
+      <c r="R37" s="31">
         <f>(1-$B$31)*P37+$B$31*Q37</f>
         <v>0.237890625</v>
       </c>
@@ -10607,15 +10612,15 @@
       <c r="O38" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="P38" s="21">
+      <c r="P38" s="34">
         <f>SUM(P33:P37)</f>
         <v>0.59681875</v>
       </c>
-      <c r="Q38" s="21">
+      <c r="Q38" s="34">
         <f>SUM(Q33:Q37)</f>
         <v>2.484875</v>
       </c>
-      <c r="R38" s="18">
+      <c r="R38" s="32">
         <f>SUM(R33:R37)</f>
         <v>0.8800271875</v>
       </c>
@@ -11137,7 +11142,7 @@
         <f t="shared" ref="C48:C57" si="1">B48</f>
         <v>0.36</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C48/20)+C48)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.6411976375</v>
       </c>
@@ -11197,7 +11202,7 @@
         <f t="shared" si="1"/>
         <v>0.6768</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C49/20)+C49)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.6802510585</v>
       </c>
@@ -11257,7 +11262,7 @@
         <f t="shared" si="1"/>
         <v>0.955584</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C50/20)+C50)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.71461806898</v>
       </c>
@@ -11317,7 +11322,7 @@
         <f t="shared" si="1"/>
         <v>1.20091392</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C51/20)+C51)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.7448610382024</v>
       </c>
@@ -11377,7 +11382,7 @@
         <f t="shared" si="1"/>
         <v>1.4168042496</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C52/20)+C52)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.771474851118112</v>
       </c>
@@ -11437,7 +11442,7 @@
         <f t="shared" si="1"/>
         <v>1.606787739648</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C53/20)+C53)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.794895006483939</v>
       </c>
@@ -11497,7 +11502,7 @@
         <f t="shared" si="1"/>
         <v>1.77397321089024</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C54/20)+C54)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.815504743205866</v>
       </c>
@@ -11557,7 +11562,7 @@
         <f t="shared" si="1"/>
         <v>1.92109642558341</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C55/20)+C55)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.833641311521162</v>
       </c>
@@ -11617,7 +11622,7 @@
         <f t="shared" si="1"/>
         <v>2.0505648545134</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C56/20)+C56)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.849601491638623</v>
       </c>
@@ -11677,7 +11682,7 @@
         <f t="shared" si="1"/>
         <v>2.16449707197179</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="31">
         <f>SUMPRODUCT((首列WILD!$B$11:$B$15*(1-C57/20)+C57)*首列WILD!$O$11:$O$15)/滚轴与赔付!$H$25</f>
         <v>0.863646450141988</v>
       </c>
@@ -11736,7 +11741,7 @@
       <c r="C58" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D58" s="21">
+      <c r="D58" s="34">
         <f>AVERAGE(D48:D57)</f>
         <v>0.770969165729209</v>
       </c>
